--- a/MOTION/Electronics.xlsx
+++ b/MOTION/Electronics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\GitHub-MOTION (Electronics-Motors)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB15E8C-D6B9-4186-B2C1-7AB126949CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536C983C-84B1-49DC-B1B3-D3519F6BB69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7695" yWindow="1635" windowWidth="19665" windowHeight="11100" xr2:uid="{343ED79C-8BC9-490C-9798-8372CAF2C348}"/>
+    <workbookView xWindow="9030" yWindow="2580" windowWidth="19665" windowHeight="11100" xr2:uid="{343ED79C-8BC9-490C-9798-8372CAF2C348}"/>
   </bookViews>
   <sheets>
     <sheet name="C2S (CONNECT-2-SOFTWARE)" sheetId="1" r:id="rId1"/>
@@ -228,7 +228,11 @@
     <t>CS008</t>
   </si>
   <si>
-    <t>In a dialog with Dresco https://github.com/grblHAL/core/issues/893#issuecomment-3796443140   
+    <t>For the actual cabling, connectors etc see CSC (Cabling-Sizing-Config)</t>
+  </si>
+  <si>
+    <t>In a dialog with Dresco (the developer of board ports of grblHAL: 
+ https://github.com/grblHAL/core/issues/893#issuecomment-3796443140   
 The outcome:
 According to the schematic &amp; the silk screen marker for pin#1, the numbering for the header should actually be;
                               10    9 GND
@@ -239,9 +243,6 @@
 Connect 1, 2, 4 to 9 (GND)
 I would work off the actual STM32 pins (PA4/5/6/7), and where they are shown in the user manual above.
 Cycle Start, Feed Hold, and Reset inputs tied to ground (to avoid having to change any settings)</t>
-  </si>
-  <si>
-    <t>For the cabling, connectors etc see CSC (Cabling-Sizing-Config)</t>
   </si>
 </sst>
 </file>
@@ -560,7 +561,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1956858" y="16506825"/>
+          <a:off x="1956858" y="16697325"/>
           <a:ext cx="4252384" cy="1428750"/>
           <a:chOff x="1956858" y="16506825"/>
           <a:chExt cx="4252384" cy="1428750"/>
@@ -1135,15 +1136,15 @@
         <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="240" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="255" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
